--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M3B1_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M3B1_IN_Piura.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.17</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>16.27</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C13" s="31">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>66.43</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>17.13</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>80.983</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1946,11 +1946,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.1399</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.17</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>80.8431</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.83</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>81.0136</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2292,6 +2292,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2500,6 +2501,7 @@
       <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="17" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -2544,6 +2546,7 @@
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="132" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -2928,11 +2931,11 @@
       </c>
       <c r="B17" s="33">
         <f>SUM(B10:B16)</f>
-        <v/>
+        <v>1261.62</v>
       </c>
       <c r="C17" s="23">
         <f>SUM(C10:C16)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -2942,19 +2945,19 @@
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17">
         <f>ROUND(AVERAGE(F10:F16),2)</f>
-        <v/>
+        <v>18.59</v>
       </c>
       <c r="G17" s="22">
         <f>ROUND(AVERAGE(G10:G16),4)</f>
-        <v/>
+        <v>0.3191</v>
       </c>
       <c r="H17" s="23">
         <f>ROUND(AVERAGE(H10:H16),2)</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="I17" s="23">
         <f>ROUND(AVERAGE(I10:I16),2)</f>
-        <v/>
+        <v>99.15</v>
       </c>
     </row>
     <row r="18"/>
